--- a/Employee_Reports_wi48/Naser Qasim Mohammad Alhaj Ahmed Q0534.xlsx
+++ b/Employee_Reports_wi48/Naser Qasim Mohammad Alhaj Ahmed Q0534.xlsx
@@ -566,11 +566,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-350</v>
+        <v>-353</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -581,53 +581,53 @@
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>14-Jul-2025</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>14-Jul-2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -652,11 +652,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
